--- a/artfynd/A 56196-2022 artfynd.xlsx
+++ b/artfynd/A 56196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126090401</v>
       </c>
       <c r="B2" t="n">
-        <v>57933</v>
+        <v>57934</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56196-2022 artfynd.xlsx
+++ b/artfynd/A 56196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126090401</v>
       </c>
       <c r="B2" t="n">
-        <v>57934</v>
+        <v>57938</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56196-2022 artfynd.xlsx
+++ b/artfynd/A 56196-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>126090401</v>
       </c>
       <c r="B2" t="n">
-        <v>57938</v>
+        <v>57939</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
